--- a/admin-panel/public/uploads/imports/import_all_leads.xlsx
+++ b/admin-panel/public/uploads/imports/import_all_leads.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,337 +440,9 @@
         <v>Import Batch</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>BABUBHAI UCHANA</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1593574862</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v>GJ03AW0406</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2011-11-13</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2011-03-15</v>
-      </c>
-      <c r="G2" t="str">
-        <v>620</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>AT RAFALESWAR,MORBI,RAJKOT,999999</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v>New</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Sonali</v>
-      </c>
-      <c r="M2" t="str">
-        <v>dummy1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>SHREE MAHESHWARI CONFECTIONERY</v>
-      </c>
-      <c r="B3" t="str">
-        <v>3214569874</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v>GJ05AU4015</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2011-11-09</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2010-11-11</v>
-      </c>
-      <c r="G3" t="str">
-        <v>600</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>SHOP NO 4 AMRAT SHILP,TIMALIYAWAD NANPURA,SURAT,395006</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>New</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Torque Sales</v>
-      </c>
-      <c r="M3" t="str">
-        <v>dummy1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ISMAILBHAI JAM</v>
-      </c>
-      <c r="B4" t="str">
-        <v>7896541236</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>GJ03AW0257</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2011-10-24</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2011-02-28</v>
-      </c>
-      <c r="G4" t="str">
-        <v>610</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>AT MALIYA,MORBI,RAJKOT,999999</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v>New</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Jiya Patel</v>
-      </c>
-      <c r="M4" t="str">
-        <v>dummy1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ANOPSINH BARIA</v>
-      </c>
-      <c r="B5" t="str">
-        <v>9632587412</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v>GJ17Y8872</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2011-10-23</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2010-11-30</v>
-      </c>
-      <c r="G5" t="str">
-        <v>1800</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>NIKALA   PO,SIMALIYA,GHOGAMBA,GHOGAMBA,999999</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>New</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Sonali</v>
-      </c>
-      <c r="M5" t="str">
-        <v>dummy1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ASHOKBHAI GOSWAMI</v>
-      </c>
-      <c r="B6" t="str">
-        <v>1478523691</v>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v>GJ03AW0160</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2011-10-11</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2011-01-28</v>
-      </c>
-      <c r="G6" t="str">
-        <v>680</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>GAYATRI MANDIR ROAD,AROGIYA NAGAR,WANKANER,999999</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v>New</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Torque Sales</v>
-      </c>
-      <c r="M6" t="str">
-        <v>dummy1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>BHARATBHAI</v>
-      </c>
-      <c r="B7" t="str">
-        <v>9876543214</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>GJ03Y0644</v>
-      </c>
-      <c r="E7" t="str">
-        <v>2011-09-18</v>
-      </c>
-      <c r="F7" t="str">
-        <v>2005-10-14</v>
-      </c>
-      <c r="G7" t="str">
-        <v>15660</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>AT PO SARVAD,TAL MALIYA MIYANA,RAJKOT,999999</v>
-      </c>
-      <c r="J7" t="str">
-        <v>agent</v>
-      </c>
-      <c r="K7" t="str">
-        <v>New</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Jiya Patel</v>
-      </c>
-      <c r="M7" t="str">
-        <v>dummy1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>GOPALBHAI GOLTAR</v>
-      </c>
-      <c r="B8" t="str">
-        <v>1234567895</v>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v>GJ03AW1118</v>
-      </c>
-      <c r="E8" t="str">
-        <v>2011-08-18</v>
-      </c>
-      <c r="F8" t="str">
-        <v>2011-03-06</v>
-      </c>
-      <c r="G8" t="str">
-        <v>680</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>BHARVAD PARA ST 6,WANKANER,RAJKOT,999999</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v>New</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Sonali</v>
-      </c>
-      <c r="M8" t="str">
-        <v>dummy1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>VANJARA HIRABHAI</v>
-      </c>
-      <c r="B9" t="str">
-        <v>9825358617</v>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>GJ17U6578</v>
-      </c>
-      <c r="E9" t="str">
-        <v>2011-03-12</v>
-      </c>
-      <c r="F9" t="str">
-        <v>2008-03-17</v>
-      </c>
-      <c r="G9" t="str">
-        <v>725</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>OTADA   SIMALIYA,GHOGAMBA,GHOGAMBA,999999</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v>New</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Torque Sales</v>
-      </c>
-      <c r="M9" t="str">
-        <v>dummy1</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M1"/>
   </ignoredErrors>
 </worksheet>
 </file>